--- a/Feuilles/Briser.xlsx
+++ b/Feuilles/Briser.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3FF6B8-1288-2142-AE99-641D8BC9F00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9229A2B0-F463-A343-945D-95C117FB22D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13880" yWindow="2560" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
+    <workbookView xWindow="6000" yWindow="2520" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>MES</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>PONT</t>
+  </si>
+  <si>
+    <t>LOOP</t>
   </si>
 </sst>
 </file>
@@ -458,13 +461,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,8 +480,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -492,7 +498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -503,7 +509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -514,7 +520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -525,7 +531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -536,7 +542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -547,7 +553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -558,7 +564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -569,7 +575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -583,7 +589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -594,7 +600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -605,7 +611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -616,7 +622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -627,7 +633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -638,7 +644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>

--- a/Feuilles/Briser.xlsx
+++ b/Feuilles/Briser.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9229A2B0-F463-A343-945D-95C117FB22D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A98439-0C4A-3D43-8681-AEAFD61F33D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6000" yWindow="2520" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -1016,7 +1016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1106,8 +1106,11 @@
       <c r="D56" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1118,7 +1121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1129,7 +1132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1140,7 +1143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1151,7 +1154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1162,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1173,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1184,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1197,8 +1200,11 @@
       <c r="D64" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1209,7 +1215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1220,7 +1226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1231,7 +1237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1242,7 +1248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1253,7 +1259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1264,7 +1270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1275,7 +1281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1288,8 +1294,11 @@
       <c r="D72" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1300,7 +1309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1311,7 +1320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1322,7 +1331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1333,7 +1342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1344,7 +1353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1355,7 +1364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1366,7 +1375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1377,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1388,7 +1397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1399,7 +1408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1412,8 +1421,11 @@
       <c r="D83" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1424,7 +1436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1435,7 +1447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1446,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1457,7 +1469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1468,7 +1480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1479,7 +1491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1490,7 +1502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1500,8 +1512,11 @@
       <c r="C91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1512,7 +1527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1523,7 +1538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1534,7 +1549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1545,7 +1560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1556,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -1567,7 +1582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1578,7 +1593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1591,8 +1606,11 @@
       <c r="D99" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1603,7 +1621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -1614,7 +1632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -1625,7 +1643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -1636,7 +1654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -1647,7 +1665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -1658,7 +1676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -1669,7 +1687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -1682,8 +1700,11 @@
       <c r="D107" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -1694,7 +1715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -1705,7 +1726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -1716,7 +1737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -1727,7 +1748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -1738,7 +1759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -1749,7 +1770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>113</v>
       </c>
@@ -1760,7 +1781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
@@ -1773,8 +1794,11 @@
       <c r="D115" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -1785,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -1796,7 +1820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
@@ -1807,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -1818,7 +1842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
@@ -1829,7 +1853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -1840,7 +1864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -1851,7 +1875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -1862,7 +1886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
@@ -1873,7 +1897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
@@ -1884,7 +1908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
@@ -1895,7 +1919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
@@ -1906,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
